--- a/기획/림버스 컴퍼니/LImbus Company (흑수 진 필두 뫼르소) 스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/LImbus Company (흑수 진 필두 뫼르소) 스킬 테이블.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1179EA8-6D23-42E3-9725-CB86E52219F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F1A63F-3725-4A92-9C97-E90FABD60D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15105" yWindow="1125" windowWidth="14085" windowHeight="14025" tabRatio="796" activeTab="3" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="11505" yWindow="7200" windowWidth="17190" windowHeight="8205" tabRatio="796" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="흑수 진 필두 뫼르소 스킬 DB" sheetId="13" r:id="rId1"/>
-    <sheet name="스킬 기본 DB" sheetId="14" r:id="rId2"/>
-    <sheet name="스킬 효과 DB" sheetId="15" r:id="rId3"/>
-    <sheet name="스킬 코인 효과 DB" sheetId="16" r:id="rId4"/>
-    <sheet name="패시브 스킬 DB" sheetId="17" r:id="rId5"/>
+    <sheet name="흑수 진 필두 뫼르소 스킬 슬롯 링크 DB" sheetId="13" r:id="rId1"/>
+    <sheet name="스킬 메인 DB" sheetId="18" r:id="rId2"/>
+    <sheet name="스킬 효과 DB" sheetId="19" r:id="rId3"/>
+    <sheet name="코인 효과 DB" sheetId="20" r:id="rId4"/>
+    <sheet name="패시브 스킬 DB" sheetId="21" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
   <si>
     <t>코인 개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -327,6 +327,274 @@
   </si>
   <si>
     <t>뇌운 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 대상 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword Target_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword Target_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Target Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_3</t>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_3</t>
+  </si>
+  <si>
+    <t>조건 키워드 ID_3</t>
+  </si>
+  <si>
+    <t>조건 키워드 형식_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword Target_3</t>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword ID_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword Type_3</t>
+  </si>
+  <si>
+    <t>활성화 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분노 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색욕 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나태 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐식 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우울 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오만 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질투 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 텍스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Activation Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrath Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lust Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sloth Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gluttony Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloom Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pride Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Envy Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect Text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 ID_2</t>
+  </si>
+  <si>
+    <t>스킬 효과 ID_3</t>
+  </si>
+  <si>
+    <t>스킬 효과 ID_4</t>
+  </si>
+  <si>
+    <t>Skill Effect ID_2</t>
+  </si>
+  <si>
+    <t>Skill Effect ID_3</t>
+  </si>
+  <si>
+    <t>Skill Effect ID_4</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_2</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_3</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_4</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_2</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_3</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_4</t>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm10M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ck07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ck04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,18 +650,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -712,114 +974,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F018BB-722B-442C-A45E-726337ED2B64}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="18.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="20.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="16.125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="21.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -831,92 +1128,266 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2F263B-B492-40CA-B655-367CD6286A54}">
-  <dimension ref="A1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{254CDFCE-DD8E-49E8-81CD-D843FE09533E}">
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="1">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="1">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -926,113 +1397,199 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7BBB97-A5B8-4BA4-8CF9-E20FB66BD2D4}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B028304-A82F-4FB8-9671-0C2E23E6AC0C}">
+  <dimension ref="A1:X3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="28.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="R1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="R2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="U2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="X2" s="1" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1042,120 +1599,281 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABFA253-2696-40F1-9903-AB41940BDB41}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012064B4-1B75-4F72-840E-E1CD049FE40B}">
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="M2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="AD2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="AE2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="AF2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="AI2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="AK2" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1165,10 +1883,139 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D636D899-B1E5-4C68-954F-C60018A5C4D9}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CD2ECC-D946-4F25-A7A2-69E0218BEE47}">
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/기획/림버스 컴퍼니/LImbus Company (흑수 진 필두 뫼르소) 스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/LImbus Company (흑수 진 필두 뫼르소) 스킬 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F1A63F-3725-4A92-9C97-E90FABD60D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5507C4-5FB8-4227-950D-78DE628C49EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11505" yWindow="7200" windowWidth="17190" windowHeight="8205" tabRatio="796" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="796" activeTab="3" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="흑수 진 필두 뫼르소 스킬 슬롯 링크 DB" sheetId="13" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="219">
   <si>
     <t>코인 개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -334,10 +334,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조건 대상 키워드 ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>조건 키워드 대상_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -350,18 +346,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>결과 대상 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Condition Keyword Target_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Condition Target Keyword ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Condition Keyword Target_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -374,10 +362,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Result Target Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>조건 키워드 대상_3</t>
   </si>
   <si>
@@ -526,10 +510,6 @@
     <t>Skill Coin Effect ID_4</t>
   </si>
   <si>
-    <t>s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -595,6 +575,318 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm20M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm20M2</t>
+  </si>
+  <si>
+    <t>altm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm30M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm30M2</t>
+  </si>
+  <si>
+    <t>05nnmm30M3</t>
+  </si>
+  <si>
+    <t>05nnmm30M4</t>
+  </si>
+  <si>
+    <t>tust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gk50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경 결과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chage Result ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm31M1</t>
+  </si>
+  <si>
+    <t>05nnmm31M2</t>
+  </si>
+  <si>
+    <t>05nnmm40M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm40M2</t>
+  </si>
+  <si>
+    <t>clvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm10C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm10C3</t>
+  </si>
+  <si>
+    <t>05nnmm10C4</t>
+  </si>
+  <si>
+    <t>05nnmm20C1</t>
+  </si>
+  <si>
+    <t>05nnmm20C2</t>
+  </si>
+  <si>
+    <t>05nnmm20C3</t>
+  </si>
+  <si>
+    <t>05nnmm30C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm30C3</t>
+  </si>
+  <si>
+    <t>05nnmm30C4</t>
+  </si>
+  <si>
+    <t>05nnmm31C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm31C2</t>
+  </si>
+  <si>
+    <t>05nnmm31C3</t>
+  </si>
+  <si>
+    <t>onht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm10C2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm20C4</t>
+  </si>
+  <si>
+    <t>05nnmm20C5</t>
+  </si>
+  <si>
+    <t>05nnmm20C6</t>
+  </si>
+  <si>
+    <t>05nnmm30C5</t>
+  </si>
+  <si>
+    <t>05nnmm30C2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm30C6</t>
+  </si>
+  <si>
+    <t>05nnmm30C7</t>
+  </si>
+  <si>
+    <t>05nnmm30C8</t>
+  </si>
+  <si>
+    <t>05nnmm30C9</t>
+  </si>
+  <si>
+    <t>ok39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gk43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm31C4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm31C5</t>
+  </si>
+  <si>
+    <t>05nnmm31C6</t>
+  </si>
+  <si>
+    <t>05nnmm31C7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gk52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05nnmm40C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_5</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_6</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_7</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_8</t>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_9</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_5</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_6</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_7</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_8</t>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID_9</t>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 자신에게 뇌기가 있으면 매턴 시작 시  자신의 충전 횟수 5 증가.
+- 자신의 충전 횟수가 10 이상이면, 일반 스킬 사용 시 충전 횟수를 3 소비하여 아래 효과 적용.
+- 마지막 코인이 대상에게 뇌기 횟수 1 부여 (턴당 2회)
+- 대상에게  뇌기가 있으면 타격 시 뇌기 횟수를 감소 시키지 않는다.
+- 일반 스킬의 마지막 코인이 뇌기를 보유한 모든 대상에게 피해량의 15% + 자신의 뇌기 잠식 횟수 1당 5% (최대 30%) 만큼의 질투 피해를 준다.
+(해당 피해는 뇌기의 타격 효과를 발동 시키지만 횟수를 감소 시키지 않는다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 자신에게 뇌운이 있으면 뇌기를 보유한 대상을 타격하거나 처치 할 될 경우 뇌기 잠식을 1 획득한다.
+(턴당 최대 3회)
+- 자신의 뇌기 잠식이 최대치가 될 경우 광폭화를 획득한다.
+- 자신에게 광폭화가 있을 때 아래 효과를 얻는다.
+-모든 일반 스킬에 가중치가 뇌기가 보유한 대상의 숫자 만큼 상승한다. (최대 3)
+-모든 일반 스킬이 사용 시 [뇌기 보유 대상 우선] 광역난사 상태가 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>홍원 군주 홍루와 존명 발동 시, 홍원 군주 홍루가 흑수환염[黑</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="새굴림"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>獣丸染</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]으로 아래 효과 얻음
+-홍원 군주의 일반 스킬 마지막 코인이 타격 시 뇌기를 부여하고 마지막 코인 피해의  15% 만큼 질투 피해를 준다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군을 타격으로 파열 피해 발동 시 타격한 아군의 충전 횟수 1 증가 (턴당 1회 발동)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +894,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,6 +919,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="새굴림"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -650,7 +950,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -659,6 +959,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -974,17 +1277,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F018BB-722B-442C-A45E-726337ED2B64}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="16.125" style="1" customWidth="1"/>
-    <col min="7" max="10" width="21.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="7" max="15" width="21.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -992,31 +1295,46 @@
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -1024,31 +1342,46 @@
         <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
@@ -1056,7 +1389,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -1064,7 +1397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>66</v>
       </c>
@@ -1072,7 +1405,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>67</v>
       </c>
@@ -1080,44 +1413,158 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>68</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1577,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{254CDFCE-DD8E-49E8-81CD-D843FE09533E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="1" bestFit="1" customWidth="1"/>
@@ -1145,7 +1592,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,7 +1627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1215,7 +1662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
@@ -1226,31 +1673,31 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>59</v>
       </c>
@@ -1261,31 +1708,31 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
@@ -1296,31 +1743,31 @@
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>61</v>
       </c>
@@ -1331,31 +1778,31 @@
         <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>68</v>
       </c>
@@ -1366,28 +1813,28 @@
         <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1398,33 +1845,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B028304-A82F-4FB8-9671-0C2E23E6AC0C}">
-  <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="21" max="21" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -1435,70 +1883,61 @@
         <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -1506,145 +1945,812 @@
         <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>144</v>
+      <c r="Q5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012064B4-1B75-4F72-840E-E1CD049FE40B}">
-  <dimension ref="A1:AL2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="31.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="26.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1661,106 +2767,58 @@
         <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AL1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -1774,106 +2832,1894 @@
         <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL2" s="1" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="A20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1884,25 +4730,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CD2ECC-D946-4F25-A7A2-69E0218BEE47}">
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="133.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1913,34 +4759,34 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1951,68 +4797,183 @@
         <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E10" s="2" t="s">
-        <v>128</v>
+      <c r="C6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
